--- a/tabular/genus/proto-refseqs-side-data.xlsx
+++ b/tabular/genus/proto-refseqs-side-data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10308"/>
   <workbookPr date1904="1" showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/robertgifford/Projects/virus/comparative/DNA/Parvovirus-GLUE/tabular/genus/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/diversity/Parvovirus-GLUE/tabular/genus/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59B3FE3B-141A-3042-AA09-D63F793328D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E32784B-98A5-7049-9B19-C00361B4A106}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20320" yWindow="3560" windowWidth="28800" windowHeight="17540" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="880" yWindow="520" windowWidth="27920" windowHeight="17500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Refset" sheetId="4" r:id="rId1"/>
@@ -1359,13 +1359,15 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="915">
     <cellStyle name="Followed Hyperlink" xfId="2" builtinId="9" hidden="1"/>
@@ -2284,7 +2286,368 @@
     <cellStyle name="Hyperlink" xfId="913" builtinId="8" hidden="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="15">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
   <colors>
     <mruColors>
@@ -2302,6 +2665,28 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{98F63F6E-7E57-8C47-89BE-5688DDC66663}" name="Table1" displayName="Table1" ref="A1:M21" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1">
+  <autoFilter ref="A1:M21" xr:uid="{53C84FF1-0E01-6647-B34F-E0F70007D6CC}"/>
+  <tableColumns count="13">
+    <tableColumn id="1" xr3:uid="{FFFE866E-4D0B-1C44-85E6-89DCB5C1EAFC}" name="sequenceID" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{1F8EB0AC-251B-124F-BC05-60F7761A9C9C}" name="virus_name" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{0451ADDC-09D0-7B48-8694-20851AC5B8A9}" name="virus_full_name" dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{A90215E6-5FFF-DB42-B113-8B3600D55081}" name="virus_other_name" dataDxfId="11"/>
+    <tableColumn id="5" xr3:uid="{1F88829F-FF80-634A-9363-3D1EC882D6B8}" name="host_species" dataDxfId="10"/>
+    <tableColumn id="6" xr3:uid="{F164865D-04CB-7A42-A402-3D1C2DBBF4EE}" name="virus_subfamily" dataDxfId="9"/>
+    <tableColumn id="7" xr3:uid="{19FA7323-F9C0-F542-B529-C90A09AFE151}" name="virus_genus" dataDxfId="8"/>
+    <tableColumn id="8" xr3:uid="{F609A298-9CC0-2F4B-91A0-F8705AADC65B}" name="assign_clade" dataDxfId="7"/>
+    <tableColumn id="9" xr3:uid="{CAD91460-6E5D-7E44-83FB-BC2BD5C3AEE1}" name="assign_subclade" dataDxfId="6"/>
+    <tableColumn id="10" xr3:uid="{E2290BA7-D4D9-B747-AC8C-AFEE9E2CE8C0}" name="virus_clade_ns" dataDxfId="5"/>
+    <tableColumn id="11" xr3:uid="{1B711142-2DE7-4241-A1BC-F28580A1D915}" name="virus_subclade_ns" dataDxfId="4"/>
+    <tableColumn id="12" xr3:uid="{BB4CF696-CCD1-594A-81D4-958D4FE6DF4F}" name="virus_clade_vp" dataDxfId="3"/>
+    <tableColumn id="13" xr3:uid="{11E547FD-A26F-7041-A14A-FA44D7D77427}" name="virus_subclade_vp" dataDxfId="2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2630,6 +3015,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
+    <col min="2" max="2" width="13.1640625" customWidth="1"/>
     <col min="3" max="3" width="39" customWidth="1"/>
     <col min="4" max="4" width="40" customWidth="1"/>
     <col min="5" max="6" width="21.33203125" customWidth="1"/>
@@ -2638,873 +3024,876 @@
     <col min="9" max="9" width="22.33203125" customWidth="1"/>
     <col min="10" max="10" width="23" customWidth="1"/>
     <col min="11" max="11" width="20.5" customWidth="1"/>
-    <col min="12" max="12" width="14.1640625" customWidth="1"/>
+    <col min="12" max="12" width="15.83203125" customWidth="1"/>
     <col min="13" max="13" width="22.1640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="4" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="M2" s="3" t="s">
+      <c r="H2" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="M2" s="5" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="M3" s="3" t="s">
+      <c r="H3" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="M3" s="5" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="M4" s="3" t="s">
+      <c r="H4" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="M4" s="5" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="M5" s="3" t="s">
+      <c r="H5" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="M5" s="5" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="F6" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="G6" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="M6" s="3" t="s">
+      <c r="H6" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="M6" s="5" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="H7" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="M7" s="3" t="s">
+      <c r="H7" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="L7" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="M7" s="5" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="F8" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G8" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="M8" s="3" t="s">
+      <c r="H8" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="M8" s="5" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="F9" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="G9" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="M9" s="3" t="s">
+      <c r="H9" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="L9" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="M9" s="5" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="F10" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="G10" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="M10" s="3" t="s">
+      <c r="H10" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="L10" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="M10" s="5" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="F11" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="G11" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="H11" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="M11" s="3" t="s">
+      <c r="H11" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="L11" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="M11" s="5" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="E12" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="F12" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="G12" s="3" t="s">
+      <c r="G12" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="M12" s="3" t="s">
+      <c r="H12" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="L12" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="M12" s="5" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="E13" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="F13" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="G13" s="3" t="s">
+      <c r="G13" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="H13" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="L13" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="M13" s="3" t="s">
+      <c r="H13" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="K13" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="L13" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="M13" s="5" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="E14" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="F14" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="G14" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="M14" s="3" t="s">
+      <c r="H14" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="J14" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="K14" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="L14" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="M14" s="5" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="E15" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="F15" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="G15" s="3" t="s">
+      <c r="G15" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="H15" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="M15" s="3" t="s">
+      <c r="H15" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="L15" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="M15" s="5" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="E16" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="F16" s="3" t="s">
+      <c r="F16" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="G16" s="3" t="s">
+      <c r="G16" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="H16" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="K16" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="L16" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="M16" s="3" t="s">
+      <c r="H16" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="K16" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="L16" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="M16" s="5" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="D17" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="E17" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="F17" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="G17" s="3" t="s">
+      <c r="G17" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="H17" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="L17" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="M17" s="3" t="s">
+      <c r="H17" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="J17" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="K17" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="L17" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="M17" s="5" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="D18" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="E18" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="F18" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="G18" s="3" t="s">
+      <c r="G18" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="M18" s="3" t="s">
+      <c r="H18" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="K18" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="L18" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="M18" s="5" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="D19" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="E19" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="F19" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="G19" s="3" t="s">
+      <c r="G19" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="H19" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="L19" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="M19" s="3" t="s">
+      <c r="H19" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="J19" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="K19" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="L19" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="M19" s="5" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D20" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="E20" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="F20" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="G20" s="3" t="s">
+      <c r="G20" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="M20" s="3" t="s">
+      <c r="H20" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="J20" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="K20" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="L20" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="M20" s="5" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C21" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="D21" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="E21" s="3" t="s">
+      <c r="E21" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="F21" s="3" t="s">
+      <c r="F21" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="G21" s="3" t="s">
+      <c r="G21" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="M21" s="3" t="s">
+      <c r="H21" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="J21" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="K21" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="L21" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="M21" s="5" t="s">
         <v>105</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
